--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_268_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_268_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M2" t="n">
         <v>15</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M3" t="n">
         <v>14</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1335,7 +1335,7 @@
         <v>2</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -1727,16 +1727,16 @@
         <v>17</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X19" t="n">
         <v>5</v>
@@ -2119,7 +2119,7 @@
         <v>6</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -2318,7 +2318,7 @@
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2903,7 +2903,7 @@
         <v>18</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -3102,7 +3102,7 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -3295,16 +3295,16 @@
         <v>21</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X27" t="n">
         <v>7</v>
@@ -3494,7 +3494,7 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -3827,16 +3827,16 @@
         <v>100</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X30" t="n">
         <v>21</v>
@@ -4292,16 +4292,16 @@
         <v>8</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X35" t="n">
         <v>3</v>
@@ -4491,7 +4491,7 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -4684,7 +4684,7 @@
         <v>19</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
@@ -5275,13 +5275,13 @@
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X40" t="n">
         <v>6</v>
@@ -5471,7 +5471,7 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -6451,13 +6451,13 @@
         <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X46" t="n">
         <v>1</v>
@@ -6784,16 +6784,16 @@
         <v>96</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="X48" t="n">
         <v>33</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_268_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_268_EL.xlsx
@@ -674,10 +674,10 @@
         <v>15</v>
       </c>
       <c r="N2" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="O2" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="P2" t="n">
         <v>7</v>
@@ -695,17 +695,17 @@
         <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V2" t="n">
         <v>8</v>
       </c>
       <c r="W2" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>60.00</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>14</v>
       </c>
       <c r="N3" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="O3" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="P3" t="n">
         <v>5</v>
@@ -851,20 +851,20 @@
         <v>6</v>
       </c>
       <c r="T3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>82.50</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -879,17 +879,17 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>50.00</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>30.00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1739,10 +1739,10 @@
         <v>2</v>
       </c>
       <c r="X19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
@@ -2951,22 +2951,22 @@
         <v>3</v>
       </c>
       <c r="AH25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="AJ25" t="n">
         <v>3</v>
       </c>
       <c r="AK25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
@@ -3111,14 +3111,14 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y26" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA26" t="n">
@@ -3307,14 +3307,14 @@
         <v>1</v>
       </c>
       <c r="X27" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y27" t="n">
         <v>7</v>
       </c>
-      <c r="Y27" t="n">
-        <v>9</v>
-      </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="AA27" t="n">
@@ -3839,14 +3839,14 @@
         <v>3</v>
       </c>
       <c r="X30" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="Y30" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -3875,22 +3875,22 @@
         <v>3</v>
       </c>
       <c r="AH30" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="AJ30" t="n">
         <v>8</v>
       </c>
       <c r="AK30" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -4304,10 +4304,10 @@
         <v>2</v>
       </c>
       <c r="X35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
@@ -4500,10 +4500,10 @@
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="Y36" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
@@ -4696,14 +4696,14 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y37" t="n">
         <v>7</v>
       </c>
-      <c r="Y37" t="n">
-        <v>8</v>
-      </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="AA37" t="n">
@@ -4892,14 +4892,14 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA38" t="n">
@@ -5284,14 +5284,14 @@
         <v>2</v>
       </c>
       <c r="X40" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y40" t="n">
         <v>6</v>
       </c>
-      <c r="Y40" t="n">
-        <v>10</v>
-      </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AA40" t="n">
@@ -5480,14 +5480,14 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y41" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA41" t="n">
@@ -5513,25 +5513,25 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL41" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
@@ -6460,14 +6460,14 @@
         <v>1</v>
       </c>
       <c r="X46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA46" t="n">
@@ -6796,14 +6796,14 @@
         <v>5</v>
       </c>
       <c r="X48" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="Y48" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>82.5%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA48" t="n">
@@ -6829,25 +6829,25 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AJ48" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK48" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL48" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
